--- a/order_forms/030_custom_t_shirt_order_form_template--order_forms.xlsx
+++ b/order_forms/030_custom_t_shirt_order_form_template--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>t_shirt_style</t>
+          <t>t_shirt_style_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Select a style</t>
+          <t>T Shirt Style 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>t_shirt_size</t>
+          <t>t_shirt_size_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Select a size</t>
+          <t>T Shirt Size 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Customer Phone</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>order_date</t>
+          <t>order_date_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Order Date</t>
+          <t>Order Date 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>t_shirt_color</t>
+          <t>t_shirt_color_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Select a color</t>
+          <t>T Shirt Color 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>customer_name</t>
+          <t>customer_name_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Customer Name</t>
+          <t>Customer Name 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>t_shirt_text</t>
+          <t>t_shirt_text_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Shirt Text</t>
+          <t>T Shirt Text 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>t_shirt_design</t>
+          <t>t_shirt_design_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Shirt Design</t>
+          <t>T Shirt Design 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>t_shirt_quantity</t>
+          <t>t_shirt_quantity_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>T Shirt Quantity 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1233,63 +1233,63 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>t_shirt_style_choices</t>
+          <t>t_shirt_style_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>t_shirt_style_choices</t>
+          <t>t_shirt_style_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>t_shirt_style_choices</t>
+          <t>t_shirt_style_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1386,19 +1386,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>t_shirt_size_choices</t>
+          <t>t_shirt_size_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>t_shirt_size_choices</t>
+          <t>t_shirt_size_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>t_shirt_color_choices</t>
+          <t>t_shirt_color_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>t_shirt_color_choices</t>
+          <t>t_shirt_color_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
